--- a/ig/nr-INS-Patient/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/ig/nr-INS-Patient/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2037" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2343" uniqueCount="391">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T12:02:48+00:00</t>
+    <t>2023-10-16T13:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -199,13 +199,206 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>HealthcareService.implicitRules</t>
+    <t>HealthcareService.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Slice based on the canonical url value</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.profile:fr-canonical</t>
+  </si>
+  <si>
+    <t>fr-canonical</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>HealthcareService.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -216,9 +409,6 @@
   </si>
   <si>
     <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
   </si>
   <si>
     <t>HealthcareService.language</t>
@@ -301,38 +491,10 @@
     <t>HealthcareService.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>HealthcareService.extension:serviceTypeDuration</t>
@@ -389,26 +551,7 @@
     <t>HealthcareService.identifier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>HealthcareService.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>HealthcareService.identifier.use</t>
@@ -457,9 +600,6 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
@@ -625,9 +765,6 @@
   </si>
   <si>
     <t>Selecting a Service Category then determines the list of relevant service types that can be selected in the primary service type.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>A category of the service(s) that could be provided.</t>
@@ -1397,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL59"/>
+  <dimension ref="A1:AL68"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.1328125" customWidth="true" bestFit="true"/>
@@ -1423,10 +1560,10 @@
     <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="57.77734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="10.26171875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="12.34765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>
@@ -1780,10 +1917,10 @@
         <v>35</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s" s="2">
         <v>60</v>
@@ -1794,9 +1931,7 @@
       <c r="M4" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="N4" t="s" s="2">
-        <v>63</v>
-      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
         <v>35</v>
@@ -1845,7 +1980,7 @@
         <v>35</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>36</v>
@@ -1854,13 +1989,13 @@
         <v>44</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>35</v>
@@ -1868,21 +2003,21 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>35</v>
@@ -1929,28 +2064,28 @@
         <v>35</v>
       </c>
       <c r="X5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB5" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Y5" t="s" s="2">
+      <c r="AC5" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="Z5" t="s" s="2">
+      <c r="AD5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE5" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="AA5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE5" t="s" s="2">
-        <v>35</v>
       </c>
       <c r="AF5" t="s" s="2">
         <v>74</v>
@@ -1959,16 +2094,16 @@
         <v>36</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>35</v>
@@ -1976,14 +2111,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -1999,19 +2134,19 @@
         <v>35</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>79</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2061,7 +2196,7 @@
         <v>35</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>36</v>
@@ -2076,7 +2211,7 @@
         <v>57</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>35</v>
@@ -2084,21 +2219,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>35</v>
@@ -2107,19 +2242,19 @@
         <v>35</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2169,22 +2304,22 @@
         <v>35</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>35</v>
@@ -2192,21 +2327,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>35</v>
@@ -2215,19 +2350,19 @@
         <v>35</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2265,34 +2400,34 @@
         <v>35</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>35</v>
@@ -2300,14 +2435,12 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>102</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>35</v>
       </c>
@@ -2325,18 +2458,20 @@
         <v>35</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>97</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>35</v>
@@ -2373,19 +2508,19 @@
         <v>35</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>36</v>
@@ -2397,10 +2532,10 @@
         <v>56</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>35</v>
@@ -2408,46 +2543,46 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>93</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>35</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>35</v>
       </c>
@@ -2456,7 +2591,7 @@
         <v>35</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="T10" t="s" s="2">
         <v>35</v>
@@ -2483,19 +2618,19 @@
         <v>35</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>36</v>
@@ -2507,10 +2642,10 @@
         <v>56</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>35</v>
@@ -2518,10 +2653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2544,15 +2679,17 @@
         <v>45</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>35</v>
@@ -2577,13 +2714,13 @@
         <v>35</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>35</v>
@@ -2616,18 +2753,18 @@
         <v>57</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>116</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2638,7 +2775,7 @@
         <v>36</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>35</v>
@@ -2647,18 +2784,20 @@
         <v>35</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>116</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>35</v>
@@ -2683,13 +2822,13 @@
         <v>35</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>35</v>
@@ -2707,22 +2846,22 @@
         <v>35</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>35</v>
@@ -2730,42 +2869,42 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="M13" t="s" s="2">
         <v>123</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2803,34 +2942,34 @@
         <v>35</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>35</v>
@@ -2838,10 +2977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2858,26 +2997,24 @@
         <v>35</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>129</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>35</v>
       </c>
@@ -2901,11 +3038,13 @@
         <v>35</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>35</v>
@@ -2923,7 +3062,7 @@
         <v>35</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>36</v>
@@ -2938,7 +3077,7 @@
         <v>57</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>35</v>
@@ -2946,14 +3085,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2969,23 +3108,21 @@
         <v>35</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>35</v>
       </c>
@@ -3009,31 +3146,31 @@
         <v>35</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>36</v>
@@ -3048,7 +3185,7 @@
         <v>57</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>35</v>
@@ -3056,21 +3193,21 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>35</v>
@@ -3079,23 +3216,21 @@
         <v>35</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="O16" t="s" s="2">
         <v>148</v>
       </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>35</v>
       </c>
@@ -3107,58 +3242,58 @@
         <v>35</v>
       </c>
       <c r="T16" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="U16" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>150</v>
-      </c>
       <c r="AG16" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>35</v>
@@ -3166,21 +3301,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>35</v>
@@ -3189,19 +3324,19 @@
         <v>35</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>153</v>
+        <v>68</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3215,7 +3350,7 @@
         <v>35</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>156</v>
+        <v>35</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>35</v>
@@ -3239,34 +3374,34 @@
         <v>35</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>35</v>
@@ -3274,12 +3409,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>35</v>
       </c>
@@ -3288,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>35</v>
@@ -3297,20 +3434,18 @@
         <v>35</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>35</v>
@@ -3359,22 +3494,22 @@
         <v>35</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>166</v>
+        <v>35</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>35</v>
@@ -3382,44 +3517,46 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>168</v>
+        <v>67</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>35</v>
       </c>
@@ -3455,34 +3592,34 @@
         <v>35</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>174</v>
+        <v>58</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>35</v>
@@ -3490,10 +3627,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3504,36 +3641,32 @@
         <v>36</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>45</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="Q20" t="s" s="2">
-        <v>180</v>
-      </c>
+      <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
         <v>35</v>
       </c>
@@ -3577,13 +3710,13 @@
         <v>35</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>56</v>
@@ -3592,18 +3725,18 @@
         <v>57</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>182</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3623,20 +3756,18 @@
         <v>35</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>184</v>
+        <v>60</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>185</v>
+        <v>61</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>35</v>
@@ -3685,7 +3816,7 @@
         <v>35</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>183</v>
+        <v>63</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>36</v>
@@ -3694,13 +3825,13 @@
         <v>44</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>173</v>
+        <v>35</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>188</v>
+        <v>64</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>35</v>
@@ -3708,21 +3839,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>190</v>
+        <v>66</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>35</v>
@@ -3731,19 +3862,19 @@
         <v>35</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>135</v>
+        <v>67</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>191</v>
+        <v>68</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>192</v>
+        <v>69</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>193</v>
+        <v>70</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3769,31 +3900,31 @@
         <v>35</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>194</v>
+        <v>35</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>189</v>
+        <v>74</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
@@ -3805,55 +3936,57 @@
         <v>56</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>197</v>
+        <v>58</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>198</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>45</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>35</v>
       </c>
@@ -3877,13 +4010,11 @@
         <v>35</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>35</v>
@@ -3901,13 +4032,13 @@
         <v>35</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>56</v>
@@ -3916,7 +4047,7 @@
         <v>57</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>35</v>
@@ -3924,10 +4055,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3938,7 +4069,7 @@
         <v>36</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>35</v>
@@ -3950,18 +4081,20 @@
         <v>45</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>35</v>
       </c>
@@ -3985,11 +4118,13 @@
         <v>35</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>35</v>
@@ -4007,13 +4142,13 @@
         <v>35</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>56</v>
@@ -4022,7 +4157,7 @@
         <v>57</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>35</v>
@@ -4030,10 +4165,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4044,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>35</v>
@@ -4056,18 +4191,20 @@
         <v>45</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>212</v>
+        <v>88</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>35</v>
       </c>
@@ -4079,7 +4216,7 @@
         <v>35</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>35</v>
+        <v>194</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>35</v>
@@ -4115,33 +4252,33 @@
         <v>35</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>173</v>
+        <v>57</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>217</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4164,16 +4301,16 @@
         <v>45</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4187,7 +4324,7 @@
         <v>35</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>35</v>
+        <v>201</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>35</v>
@@ -4223,7 +4360,7 @@
         <v>35</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>36</v>
@@ -4238,7 +4375,7 @@
         <v>57</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>35</v>
@@ -4246,10 +4383,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4272,16 +4409,16 @@
         <v>45</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>118</v>
+        <v>205</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4331,7 +4468,7 @@
         <v>35</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>36</v>
@@ -4343,10 +4480,10 @@
         <v>56</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>57</v>
+        <v>210</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>35</v>
@@ -4354,10 +4491,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4377,19 +4514,19 @@
         <v>35</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4439,7 +4576,7 @@
         <v>35</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>36</v>
@@ -4451,10 +4588,10 @@
         <v>56</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>35</v>
@@ -4462,10 +4599,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4482,28 +4619,30 @@
         <v>35</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>45</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="Q29" s="2"/>
+      <c r="Q29" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="R29" t="s" s="2">
         <v>35</v>
       </c>
@@ -4547,7 +4686,7 @@
         <v>35</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>36</v>
@@ -4559,21 +4698,21 @@
         <v>56</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>239</v>
+        <v>57</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>35</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4584,7 +4723,7 @@
         <v>36</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>35</v>
@@ -4593,19 +4732,19 @@
         <v>35</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4655,22 +4794,22 @@
         <v>35</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>35</v>
@@ -4678,21 +4817,21 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>35</v>
@@ -4701,19 +4840,19 @@
         <v>35</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4739,13 +4878,13 @@
         <v>35</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>35</v>
+        <v>239</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>35</v>
@@ -4763,7 +4902,7 @@
         <v>35</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>36</v>
@@ -4775,25 +4914,25 @@
         <v>56</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>173</v>
+        <v>57</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>35</v>
+        <v>242</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>35</v>
+        <v>244</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4809,19 +4948,19 @@
         <v>35</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4847,13 +4986,13 @@
         <v>35</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>194</v>
+        <v>117</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>35</v>
@@ -4871,7 +5010,7 @@
         <v>35</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>36</v>
@@ -4886,7 +5025,7 @@
         <v>57</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>35</v>
@@ -4894,10 +5033,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4917,18 +5056,20 @@
         <v>35</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>260</v>
+        <v>181</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>35</v>
@@ -4953,13 +5094,11 @@
         <v>35</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>35</v>
+        <v>254</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>35</v>
@@ -4977,7 +5116,7 @@
         <v>35</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>36</v>
@@ -4992,7 +5131,7 @@
         <v>57</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>35</v>
@@ -5000,10 +5139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5014,7 +5153,7 @@
         <v>36</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>35</v>
@@ -5023,18 +5162,20 @@
         <v>35</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>118</v>
+        <v>256</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>119</v>
+        <v>257</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>35</v>
@@ -5083,44 +5224,44 @@
         <v>35</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>121</v>
+        <v>255</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>35</v>
+        <v>218</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>35</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>35</v>
@@ -5129,19 +5270,19 @@
         <v>35</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>93</v>
+        <v>263</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>123</v>
+        <v>264</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>95</v>
+        <v>265</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5179,34 +5320,34 @@
         <v>35</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>124</v>
+        <v>262</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>58</v>
+        <v>266</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>35</v>
@@ -5214,46 +5355,44 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>266</v>
+        <v>35</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>45</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>35</v>
       </c>
@@ -5301,22 +5440,22 @@
         <v>35</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>58</v>
+        <v>271</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>35</v>
@@ -5324,10 +5463,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5350,16 +5489,16 @@
         <v>35</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>135</v>
+        <v>273</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>203</v>
+        <v>276</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5385,10 +5524,10 @@
         <v>35</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>194</v>
+        <v>35</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>273</v>
+        <v>35</v>
       </c>
       <c r="Z37" t="s" s="2">
         <v>35</v>
@@ -5409,7 +5548,7 @@
         <v>35</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>36</v>
@@ -5424,7 +5563,7 @@
         <v>57</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>35</v>
@@ -5432,10 +5571,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5455,19 +5594,19 @@
         <v>35</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>229</v>
+        <v>279</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5517,7 +5656,7 @@
         <v>35</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>36</v>
@@ -5529,10 +5668,10 @@
         <v>56</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>57</v>
+        <v>283</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>35</v>
@@ -5540,10 +5679,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5566,16 +5705,16 @@
         <v>35</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>135</v>
+        <v>286</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5601,13 +5740,13 @@
         <v>35</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>194</v>
+        <v>35</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>283</v>
+        <v>35</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>284</v>
+        <v>35</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>35</v>
@@ -5625,7 +5764,7 @@
         <v>35</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>36</v>
@@ -5637,10 +5776,10 @@
         <v>56</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>57</v>
+        <v>290</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>35</v>
@@ -5648,10 +5787,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5674,16 +5813,16 @@
         <v>35</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>135</v>
+        <v>256</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5709,10 +5848,10 @@
         <v>35</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>194</v>
+        <v>35</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>290</v>
+        <v>35</v>
       </c>
       <c r="Z40" t="s" s="2">
         <v>35</v>
@@ -5733,7 +5872,7 @@
         <v>35</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>36</v>
@@ -5745,10 +5884,10 @@
         <v>56</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>35</v>
@@ -5756,10 +5895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5782,16 +5921,16 @@
         <v>35</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5817,13 +5956,13 @@
         <v>35</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>72</v>
+        <v>299</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>73</v>
+        <v>301</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>35</v>
@@ -5841,7 +5980,7 @@
         <v>35</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>36</v>
@@ -5856,7 +5995,7 @@
         <v>57</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>35</v>
@@ -5864,10 +6003,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5890,17 +6029,15 @@
         <v>35</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>135</v>
+        <v>304</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>35</v>
@@ -5925,13 +6062,13 @@
         <v>35</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>194</v>
+        <v>35</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>299</v>
+        <v>35</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>300</v>
+        <v>35</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>35</v>
@@ -5949,7 +6086,7 @@
         <v>35</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>36</v>
@@ -5964,7 +6101,7 @@
         <v>57</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>285</v>
+        <v>64</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>35</v>
@@ -5972,10 +6109,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5998,13 +6135,13 @@
         <v>35</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>176</v>
+        <v>60</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>302</v>
+        <v>61</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>303</v>
+        <v>62</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6055,7 +6192,7 @@
         <v>35</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>301</v>
+        <v>63</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>36</v>
@@ -6064,13 +6201,13 @@
         <v>44</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>285</v>
+        <v>64</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>35</v>
@@ -6078,14 +6215,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6104,16 +6241,16 @@
         <v>35</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>260</v>
+        <v>67</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>305</v>
+        <v>68</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>306</v>
+        <v>69</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>307</v>
+        <v>70</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6151,19 +6288,19 @@
         <v>35</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>304</v>
+        <v>74</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>36</v>
@@ -6175,10 +6312,10 @@
         <v>56</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>308</v>
+        <v>58</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>35</v>
@@ -6193,35 +6330,39 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>35</v>
+        <v>310</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>119</v>
+        <v>311</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>35</v>
       </c>
@@ -6269,22 +6410,22 @@
         <v>35</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>121</v>
+        <v>313</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>35</v>
@@ -6292,21 +6433,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>35</v>
@@ -6318,16 +6459,16 @@
         <v>35</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>92</v>
+        <v>181</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>93</v>
+        <v>315</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>123</v>
+        <v>316</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>95</v>
+        <v>247</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6353,10 +6494,10 @@
         <v>35</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>35</v>
+        <v>317</v>
       </c>
       <c r="Z46" t="s" s="2">
         <v>35</v>
@@ -6365,34 +6506,34 @@
         <v>35</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>124</v>
+        <v>314</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>58</v>
+        <v>302</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>35</v>
@@ -6400,46 +6541,44 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>266</v>
+        <v>35</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>92</v>
+        <v>273</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>267</v>
+        <v>319</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>268</v>
+        <v>320</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>35</v>
       </c>
@@ -6487,22 +6626,22 @@
         <v>35</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>269</v>
+        <v>318</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>58</v>
+        <v>322</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>35</v>
@@ -6510,10 +6649,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6536,16 +6675,16 @@
         <v>35</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>221</v>
+        <v>326</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6571,11 +6710,13 @@
         <v>35</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>35</v>
@@ -6593,7 +6734,7 @@
         <v>35</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>36</v>
@@ -6608,7 +6749,7 @@
         <v>57</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>35</v>
@@ -6616,10 +6757,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6630,7 +6771,7 @@
         <v>36</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>35</v>
@@ -6642,15 +6783,17 @@
         <v>35</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>35</v>
@@ -6675,10 +6818,10 @@
         <v>35</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>35</v>
+        <v>334</v>
       </c>
       <c r="Z49" t="s" s="2">
         <v>35</v>
@@ -6699,13 +6842,13 @@
         <v>35</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>56</v>
@@ -6714,7 +6857,7 @@
         <v>57</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>35</v>
@@ -6722,10 +6865,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6736,7 +6879,7 @@
         <v>36</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>35</v>
@@ -6748,16 +6891,16 @@
         <v>35</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>320</v>
+        <v>181</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6783,13 +6926,13 @@
         <v>35</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>35</v>
@@ -6807,13 +6950,13 @@
         <v>35</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>56</v>
@@ -6822,7 +6965,7 @@
         <v>57</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>35</v>
@@ -6830,10 +6973,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6844,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>35</v>
@@ -6856,16 +6999,16 @@
         <v>35</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>320</v>
+        <v>181</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>323</v>
+        <v>247</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -6891,13 +7034,13 @@
         <v>35</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>35</v>
+        <v>343</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>35</v>
+        <v>344</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>35</v>
@@ -6915,13 +7058,13 @@
         <v>35</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>56</v>
@@ -6930,7 +7073,7 @@
         <v>57</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>35</v>
@@ -6938,10 +7081,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6952,7 +7095,7 @@
         <v>36</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>35</v>
@@ -6964,13 +7107,13 @@
         <v>35</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>260</v>
+        <v>221</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7021,13 +7164,13 @@
         <v>35</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>56</v>
@@ -7036,7 +7179,7 @@
         <v>57</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>35</v>
@@ -7044,10 +7187,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7058,7 +7201,7 @@
         <v>36</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>35</v>
@@ -7070,15 +7213,17 @@
         <v>35</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>118</v>
+        <v>304</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>119</v>
+        <v>349</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>35</v>
@@ -7127,22 +7272,22 @@
         <v>35</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>121</v>
+        <v>348</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>65</v>
+        <v>352</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>35</v>
@@ -7150,21 +7295,21 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>35</v>
@@ -7176,17 +7321,15 @@
         <v>35</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>95</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>35</v>
@@ -7223,34 +7366,34 @@
         <v>35</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>35</v>
@@ -7258,14 +7401,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>266</v>
+        <v>66</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7278,26 +7421,24 @@
         <v>35</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>267</v>
+        <v>68</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>268</v>
+        <v>69</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>35</v>
       </c>
@@ -7333,19 +7474,19 @@
         <v>35</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>269</v>
+        <v>74</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>36</v>
@@ -7357,7 +7498,7 @@
         <v>56</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>58</v>
@@ -7368,44 +7509,46 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>35</v>
+        <v>310</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>35</v>
       </c>
@@ -7453,22 +7596,22 @@
         <v>35</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>35</v>
@@ -7476,10 +7619,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7490,7 +7633,7 @@
         <v>36</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>35</v>
@@ -7502,16 +7645,16 @@
         <v>35</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>163</v>
+        <v>265</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7537,13 +7680,11 @@
         <v>35</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>35</v>
+        <v>359</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>35</v>
@@ -7561,22 +7702,22 @@
         <v>35</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>308</v>
+        <v>352</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>35</v>
@@ -7584,10 +7725,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7610,17 +7751,15 @@
         <v>35</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>118</v>
+        <v>221</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>35</v>
@@ -7669,7 +7808,7 @@
         <v>35</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>36</v>
@@ -7684,7 +7823,7 @@
         <v>57</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>308</v>
+        <v>352</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>35</v>
@@ -7692,10 +7831,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7706,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>35</v>
@@ -7718,16 +7857,16 @@
         <v>35</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>215</v>
+        <v>367</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7777,24 +7916,994 @@
         <v>35</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>173</v>
+        <v>57</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AL68" t="s" s="2">
         <v>35</v>
       </c>
     </row>
